--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Options" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Room odds" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Event script" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Options" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Room odds" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,18 +32,25 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="000000FF"/>
     </font>
   </fonts>
   <fills count="4">
@@ -55,16 +62,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F6228"/>
+        <fgColor rgb="FF4F6228"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -74,23 +81,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -112,9 +125,24 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -497,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -507,10 +535,11 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -548,11 +577,16 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>What it does, exactly</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Your notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="99.75" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -575,15 +609,24 @@
         <v>1</v>
       </c>
       <c r="F2" s="4">
-        <f>E2/SUM($E$2:$E$15)</f>
+        <f>E2/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" s="5" t="n"/>
-    </row>
-    <row r="3">
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Pay 60 Leaves: a purple seal on 1 random spell that can still be sealed (that spell needs 1 Essence less). Greyed out if you have under 60 Leaves. (2) Heal 12 HP (never above your max). (3) Nothing.</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Choose 1: Pay 50 leaves (Gain 2 random bottles - The well seems pleased with your leaves ) 2) Drink from it (The well was not pleased with that - Poison 3 next fight). 3) Jump in (You found a cursed artifact, with the price of your broken leg (take 15 damage))</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="142.5" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -599,22 +642,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>A tiny wind sprite is crying under a leaf. It swears it knows a great spell, if you can get it home.</t>
+          <t>A tiny wind sprite is crying under a leaf. It said that a mean monster has taken over his house and begs you for help</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="4">
-        <f>E3/SUM($E$2:$E$15)</f>
+        <f>E3/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4">
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>1) Help him confont the monster (immediately get into a mini boss fight, the wind sprite gives you 2 air to start the fight. Text: The monster is indeed very mean. Your new found friend tried his best to help you, which is not much). 2) Refuse to help (The wind sprite stopped crying, for he understood that it would do him no good and no one is going to help him (nothing happens to the player)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -630,22 +678,31 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Glowing mushrooms form a perfect circle. Folk tales are very clear about what happens if you dance in one. Unfortunately, they disagree.</t>
+          <t>Glowing mushrooms form a perfect circle. They looks pretty edible and you are hungry</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="4">
-        <f>E4/SUM($E$2:$E$15)</f>
+        <f>E4/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5">
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) 50/50: heal to full HP, or an ambush fight starts right away. (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Choices: Eat a mushroom (50% loses 5HP (text say: It was poisonous) or heal 5HP 49% (it was edible) or gain 20 max HP(1%, it was miraculous). Or walk away (nothing) </t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="99.75" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -668,15 +725,24 @@
         <v>0.4</v>
       </c>
       <c r="F5" s="4">
-        <f>E5/SUM($E$2:$E$15)</f>
+        <f>E5/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Choose one price, all for 1 random normal artifact you don't own (nothing if there's none left): (1) Lose 12 max HP (greyed out unless your max HP is over 17). (2) Lose 2 random spells from your spellbook for good (you always keep at least 1). (3) 2 random spells each need 1 more random Essence at the end of their pattern, for the run. (4) Nothing. Rarer than most events (weight 0.4).</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>1) reach in (50% found a random bottle, 25% found 30 leaves. 20% take 5 damage, 5% find an artifact) 2) Throw in a bottle (it hit something mean: trigger a fight - 50%) (nothing happens 10%). 40% They throw back 3 bottles  (leave us alone. Git)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="171" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -692,22 +758,31 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>A bard with a lute made of antlers offers to teach you a song of legend. For a fee, naturally.</t>
+          <t>A bard with a lute made of antlers ask you what do you think of his lute</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <f>E6/SUM($E$2:$E$15)</f>
+        <f>E6/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7">
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Pay 35 Leaves: learn a random Legendary spell you've unlocked and don't have yet; if there is none you keep your Leaves. (2) Heal 5 HP.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>1) That's animal cruelty (he is mad and play the flute furiously, it attracted the enrage rolling bear!: start a fight with the enraged rolling bear) 2) It is beautiful (The bard is pleased with a complement and played you a beautiful song: heal 10). 3) Can I have it? (The bard said yes, for a price: 100 leaves (you get his flute! Artifact (every 10 chants, apply 2 weaks on all enemies) or, actually I don't have that much (He seems disappointed but nod at you politely - nothing happens).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="99.75" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -723,22 +798,31 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>A grinning idol sits on a heap of golden leaves. The leaves are lovely. The grin is not.</t>
+          <t>A grinning idol sits on a heap of golden leaves. Inside its mouth hide a black box.</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="F7" s="4">
-        <f>E7/SUM($E$2:$E$15)</f>
+        <f>E7/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8">
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Gain 1 random cursed artifact you don't own (+0 Leaves). (2) Heal 8 HP. Rarer than most events (weight 0.4).</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Pry the box from its mouth (lose 10HP, gain a random curse artifact). 2) Take the leaves (lose 10 HP, gain 50 leaves). 3) put some more leaves down (cost 100 leaves, gain a random artifact. The idol seems pleased and drop the box from its yaw).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28.5" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -761,15 +845,20 @@
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <f>E8/SUM($E$2:$E$15)</f>
+        <f>E8/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9">
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Lose 5 HP: +45 Leaves. Greyed out unless you have more than 5 HP. (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="28.5" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -792,13 +881,18 @@
         <v>1</v>
       </c>
       <c r="F9" s="4">
-        <f>E9/SUM($E$2:$E$15)</f>
+        <f>E9/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="5" t="n"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Lose 10 max HP: purple seals on 2 random spells (each needs 1 Essence less). Greyed out unless your max HP is over 15. (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -823,15 +917,20 @@
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <f>E10/SUM($E$2:$E$15)</f>
+        <f>E10/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11">
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Pay 25 Leaves: +6 max HP (and +6 HP). (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="28.5" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -854,15 +953,20 @@
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <f>E11/SUM($E$2:$E$15)</f>
+        <f>E11/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12">
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Pay 40 Leaves: 1 random artifact of yours that has a + version becomes its + version. Greyed out if none can be upgraded. (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="42.75" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -885,15 +989,20 @@
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <f>E12/SUM($E$2:$E$15)</f>
+        <f>E12/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13">
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Pick 2 of your artifacts of the same tier and give them away, then pick 1 of 3 artifacts of the next tier up. Backing out at any step cancels the trade. Greyed out if you have no pair to trade. (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="28.5" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -916,15 +1025,20 @@
         <v>1</v>
       </c>
       <c r="F13" s="4">
-        <f>E13/SUM($E$2:$E$15)</f>
+        <f>E13/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14">
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Heal 10 HP. (2) +30 Leaves. (3) 1 random bottle (only if a bottle slot is free).</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="42.75" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -947,15 +1061,20 @@
         <v>1</v>
       </c>
       <c r="F14" s="4">
-        <f>E14/SUM($E$2:$E$15)</f>
+        <f>E14/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15">
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Pick a spell (not a Power) and lose half your current HP (rounded down): for the rest of the run that spell plays as an anti-spell (or an anti-spell as a normal spell). Greyed out under 2 HP. (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="28.5" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -978,32 +1097,73 @@
         <v>1</v>
       </c>
       <c r="F15" s="4">
-        <f>E15/SUM($E$2:$E$15)</f>
+        <f>E15/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Pay 25 Leaves: 2 random bottles (as many as your free slots hold; slots full: you keep your Leaves). (2) Lose 3 HP: 1 random bottle. (3) Nothing.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="57" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>note_to_self</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>A Note to Yourself</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>A folded note is pinned to a tree, in handwriting you know very well. "Thought you might need this. Leave one for next time."</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <f>E16/SUM($E$2:$E$16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Choose one: (1) Take the spell waiting in the note into your spellbook (and active row if there's room), then pick one of your spells (not a fused one) to leave in the note: it leaves your spellbook and is kept in the save file, so a later run finds it. It's stored plain (no seals, curses or inversion). The very first note on a save holds Aole's Blessing. (2) Nothing.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Blue text = values you can change. Yellow = your notes. Black = from the game / formulas.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Source: scripts/core/map_events.gd (exported 2026-10-14).</t>
+          <t>Blue text = values you can change. Yellow = your notes. Black = from the game / formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Source: scripts/core/map_events.gd (+ what each option does: RunState._do_event_option and the pick screens in main.gd), updated 2026-10-29.</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1179,1835 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Acts</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Button text (shown before choosing)</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Greyed out / asks for</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Result text (shown after choosing)</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>What actually happens (hidden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Toss in 50 Leaves</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>greyed out under 50 Leaves</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>The well seems pleased with your leaves. Two bottles float up to the surface for you.</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>+2 random bottles (too many: the swap screen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Drink from it</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>The well was not pleased with that. Your stomach turns, and it will still be turning when your next fight starts.</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Poison 3 when your next fight starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>well</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Jump in</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>At the bottom you find a cursed artifact, at the price of a broken leg.</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>lose 15 HP (can kill); a random cursed artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>lost_sprite</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Help him confront the monster</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>The monster is indeed very mean. Your new friend tries his best to help you, which is not much: a little breeze, 2 Air to start the fight.</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>fight: a random elite of this act; you start it with A A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>lost_sprite</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Refuse to help</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>The wind sprite stops crying. He understands that it would do him no good, and that no one is going to help him.</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>mushroom_ring</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Eat a mushroom</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>It was poisonous. You lose 5 HP.</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>lose 5 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>mushroom_ring</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Eat a mushroom</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="15" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>It was edible, and quite tasty. You heal 5 HP.</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>heal 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>mushroom_ring</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Eat a mushroom</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>It was miraculous! You feel stronger than ever: +20 max HP, and you heal 20.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>+20 max HP and heal 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>mushroom_ring</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>You leave the mushrooms for someone hungrier.</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Reach in</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Your fingers close around a little bottle.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>+1 random bottles (too many: the swap screen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Reach in</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>You pull out a handful of golden leaves: 30 Leaves.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>+30 Leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Reach in</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Something bites you, hard. You lose 5 HP.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>lose 5 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Reach in</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Deep inside, something old and precious: an artifact!</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>a random normal artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Throw in a bottle</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>you pick a bottle to give away; greyed out with none</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Your bottle hits something mean. It is coming out, and it is not happy.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>fight: a random monster of this act</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Throw in a bottle</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>you pick a bottle to give away; greyed out with none</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>You hear it shatter somewhere deep down. Then nothing at all.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Throw in a bottle</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>you pick a bottle to give away; greyed out with none</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>"Hey! Y'all quit chuckin' things in here! Here, take 'em back!" Three broken bottles come flyin' out of the stump. "Now leave us alone. Git!"</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>+3 broken_bottle (too many: the swap screen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>hollow_stump</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr"/>
+      <c r="F18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Whatever lives in there can keep its shiny thing.</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>bard</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>That's animal cruelty!</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr"/>
+      <c r="F19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>He is furious, and plays his lute furiously. The racket wakes up an Enraged Rolling Bear!</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>fight: enraged_bear (elite rewards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>bard</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>It is beautiful</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr"/>
+      <c r="F20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>The bard is pleased with the compliment and plays you a beautiful song. You heal 10 HP.</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>heal 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>bard</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Can I have it?</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>The bard says yes. For a price, of course: 100 Leaves.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>bard</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Pay 100 Leaves</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>greyed out under 100 Leaves</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>He hands you his lute with a little sigh. It is yours now: A Nice Lute.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>the artifact nice_lute</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>bard</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Actually, I don't have that much</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr"/>
+      <c r="F23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>He seems disappointed, but nods at you politely.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>cursed_shrine</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Pry the box from its mouth</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr"/>
+      <c r="F24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Its jaw snaps shut on your hand as you pull the box free. You lose 10 HP. Inside the box: a cursed artifact.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>lose 10 HP (can kill); a random cursed artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>cursed_shrine</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Take the leaves</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>The idol bites you as you scoop up the leaves. You lose 10 HP, and gain 50 Leaves.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>lose 10 HP (can kill); +50 Leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>cursed_shrine</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Put down 100 more Leaves</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>greyed out under 100 Leaves</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>The idol seems pleased, and drops the box from its jaw. Inside: an artifact.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>a random normal artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>amber_vein</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Reach in (lose 5 HP): +45 Leaves</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr"/>
+      <c r="F27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>amber_vein</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Admire it and move on</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr"/>
+      <c r="F28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>old_tome</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Read it (lose 10 max HP): 2 random spells need 1 Essence less</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr"/>
+      <c r="F29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>old_tome</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Close it gently</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>squirrel</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Buy it for 25 Leaves (+6 max HP)</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr"/>
+      <c r="F31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>max_hp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>squirrel</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Politely decline</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr"/>
+      <c r="F32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>tinker</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Pay 40 Leaves: upgrade a random artifact</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr"/>
+      <c r="F33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>upgrade_artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>tinker</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>No thank you</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr"/>
+      <c r="F34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>barterer</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Trade 2 artifacts of the same tier for 1 of the next tier</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr"/>
+      <c r="F35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>trade_artifacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>barterer</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Keep what you have</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr"/>
+      <c r="F36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>lost_camp</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Rest by the fire (heal 10)</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr"/>
+      <c r="F37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>lost_camp</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Search the pouch (+30 Leaves)</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr"/>
+      <c r="F38" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>lost_camp</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Check the saddlebag (a random bottle)</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr"/>
+      <c r="F39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>bottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>inverted_pool</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Let it drink half your HP: invert a spell (a spell becomes an anti-spell, an anti-spell a spell)</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr"/>
+      <c r="F40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>invert_spell</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>inverted_pool</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Step back from the edge</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr"/>
+      <c r="F41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>apothecary</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Pay 25 Leaves: 2 random bottles</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr"/>
+      <c r="F42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>bottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>apothecary</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Ask for a free sample (lose 3 HP): a random bottle</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr"/>
+      <c r="F43" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>bottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>apothecary</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Walk on</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>note_to_self</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Take the spell in the note, and leave one of yours in it</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr"/>
+      <c r="F45" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>note_swap</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>note_to_self</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Leave the note for another day</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr"/>
+      <c r="F46" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>(not written yet: old event, shows the button's numbers)</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>farmer_farm</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Of course</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr"/>
+      <c r="F47" s="14" t="inlineStr"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>"Bless you!" The farmer is on his feet at once. "They're goblins. They pop up out of the wheat to nibble the ears, then duck back down. Shoot every one you see and I'll give you a Leaf a head. The big ones are hobgoblins: they take three shots, but they're worth 5 apiece. But mind the green ones! Those are the fairies who look after my fields, and every one you shoot will cost you 2 Leaves. You've got one minute before they eat the lot."</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>farmer_farm</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr"/>
+      <c r="F48" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>(the mini game, then the farmer tallies how many goblins, hobgoblins and fairies, and the Leaves)</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>60 s shooting in the wheat: goblin +1, hobgoblin (3 shots) +5, fairy -2 Leaves; fairies 20% of the heads at the start, 35% at the end; never below 0 Leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>farmer_farm</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>No way! I'm too busy to deal with peasants' problems</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr"/>
+      <c r="F49" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>"I see," says the farmer quietly, and goes back to staring at his wheat. You walk on.</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Built from scripts/core/map_events.gd (the user's notes on the Events tab are canon). Blue = wording and numbers you can change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Events 7-15 are still the old ones (to be rewritten later): their buttons still show what they do.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1092,7 +3080,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>well</t>
@@ -1422,7 +3410,7 @@
       </c>
       <c r="K9" s="5" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="28.5" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>hollow_stump</t>
@@ -1467,7 +3455,7 @@
       </c>
       <c r="K10" s="5" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="28.5" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>hollow_stump</t>
@@ -1801,7 +3789,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="5" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="28.5" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>old_tome</t>
@@ -1965,7 +3953,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="5" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="28.5" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>tinker</t>
@@ -2045,7 +4033,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="5" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="28.5" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>barterer</t>
@@ -2246,7 +4234,7 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="5" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="28.5" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>inverted_pool</t>
@@ -2328,7 +4316,7 @@
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="5" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="28.5" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>apothecary</t>
@@ -2371,7 +4359,7 @@
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="5" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="28.5" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>apothecary</t>
@@ -2414,7 +4402,7 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="5" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="28.5" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>apothecary</t>
@@ -2452,13 +4440,91 @@
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="28.5" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>note_to_self</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A Note to Yourself</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Take the spell in the note, and leave one of yours in it</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>note_swap</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Get the save's stored spell; store one of yours (pick) for a later run</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>note_to_self</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>A Note to Yourself</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Leave the note for another day</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -2534,21 +2534,25 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>Rest by the fire (heal 10)</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr"/>
+          <t>Half-cook some spells</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>greyed out without 2 spells that can be fused</t>
+        </is>
+      </c>
       <c r="F37" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>The fire sputters out before your spells are quite done. They are fused all the same, but no wax came of it.</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>heal</t>
+          <t>the campfire's fusing of 2 spells, but no wax seal</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2564,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -2570,28 +2574,28 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Search the pouch (+30 Leaves)</t>
+          <t>Rest restlessly</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr"/>
-      <c r="F38" s="14" t="n">
+      <c r="F38" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>You toss and turn on the lumpy ground, and wake up stiff all over. Still, it helped a little: you heal {n} HP.</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>amber</t>
+          <t>heal half a campfire rest (15% of max HP, rounded down)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>lost_camp</t>
+          <t>inverted_pool</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -2601,12 +2605,12 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>Check the saddlebag (a random bottle)</t>
+          <t>Let it drink half your HP: invert a spell (a spell becomes an anti-spell, an anti-spell a spell)</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr"/>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>bottle</t>
+          <t>invert_spell</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2641,12 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Let it drink half your HP: invert a spell (a spell becomes an anti-spell, an anti-spell a spell)</t>
+          <t>Step back from the edge</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr"/>
@@ -2656,14 +2660,14 @@
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>invert_spell</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>inverted_pool</t>
+          <t>apothecary</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -2673,12 +2677,12 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>Step back from the edge</t>
+          <t>Pay 25 Leaves: 2 random bottles</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr"/>
@@ -2692,7 +2696,7 @@
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>bottle</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2713,12 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Pay 25 Leaves: 2 random bottles</t>
+          <t>Ask for a free sample (lose 3 HP): a random bottle</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr"/>
@@ -2745,12 +2749,12 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>Ask for a free sample (lose 3 HP): a random bottle</t>
+          <t>Walk on</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr"/>
@@ -2764,14 +2768,14 @@
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>bottle</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>apothecary</t>
+          <t>note_to_self</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -2781,12 +2785,12 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Walk on</t>
+          <t>Take the spell in the note, and leave one of yours in it</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr"/>
@@ -2800,7 +2804,7 @@
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>note_swap</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2821,12 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>Take the spell in the note, and leave one of yours in it</t>
+          <t>Leave the note for another day</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr"/>
@@ -2836,14 +2840,14 @@
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>note_swap</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>note_to_self</t>
+          <t>farmer_farm</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -2853,26 +2857,24 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Leave the note for another day</t>
+          <t>Of course</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="F46" s="14" t="inlineStr"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>"Bless you!" The farmer is on his feet at once. "They're goblins. They pop up out of the wheat to nibble the ears, then duck back down. Shoot every one you see and I'll give you a Leaf a head. The big ones are hobgoblins: they take three shots, but they're worth 5 apiece. But mind the green ones! Those are the fairies who look after my fields, and every one you shoot will cost you 2 Leaves. You've got one minute before they eat the lot."</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>opens a second page</t>
         </is>
       </c>
     </row>
@@ -2889,24 +2891,26 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>Of course</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr"/>
-      <c r="F47" s="14" t="inlineStr"/>
+      <c r="F47" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>"Bless you!" The farmer is on his feet at once. "They're goblins. They pop up out of the wheat to nibble the ears, then duck back down. Shoot every one you see and I'll give you a Leaf a head. The big ones are hobgoblins: they take three shots, but they're worth 5 apiece. But mind the green ones! Those are the fairies who look after my fields, and every one you shoot will cost you 2 Leaves. You've got one minute before they eat the lot."</t>
+          <t>(the mini game, then the farmer tallies how many goblins, hobgoblins and fairies, and the Leaves)</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>opens a second page</t>
+          <t>60 s shooting in the wheat: goblin +1, hobgoblin (3 shots) +5, fairy -2 Leaves; fairies 20% of the heads at the start, 35% at the end; never below 0 Leaves</t>
         </is>
       </c>
     </row>
@@ -2923,33 +2927,33 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>No way! I'm too busy to deal with peasants' problems</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr"/>
-      <c r="F48" s="14" t="n">
+      <c r="F48" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>(the mini game, then the farmer tallies how many goblins, hobgoblins and fairies, and the Leaves)</t>
+          <t>"I see," says the farmer quietly, and goes back to staring at his wheat. You walk on.</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>60 s shooting in the wheat: goblin +1, hobgoblin (3 shots) +5, fairy -2 Leaves; fairies 20% of the heads at the start, 35% at the end; never below 0 Leaves</t>
+          <t>nothing</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>farmer_farm</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -2959,40 +2963,1871 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Ignite a spell to burn a way out</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>the spell you picked is gone for the run</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>No way! I'm too busy to deal with peasants' problems</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr"/>
-      <c r="F49" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>"I see," says the farmer quietly, and goes back to staring at his wheat. You walk on.</t>
-        </is>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Force your way out</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr"/>
+      <c r="F50" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>lose 5 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Follow the voice</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr"/>
+      <c r="F51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>You squeeze between the cacti towards the humming. The spines catch you on the way: you lose {n} HP. The voice is closer now, but so are the walls.</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>lose 1-3 HP at random (can kill); then the same choices again</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Ignite a spell to burn a way out</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>the spell you picked is gone for the run</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>Force your way out</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr"/>
+      <c r="F53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>lose 5 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Follow the voice</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr"/>
+      <c r="F54" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>Deeper still. More spines, another {n} HP. The humming has turned into words you can almost understand.</t>
+        </is>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>lose 1-3 HP at random (can kill); then the same choices again</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>3.3.1</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Ignite a spell to burn a way out</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>the spell you picked is gone for the run</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>3.3.2</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Force your way out</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr"/>
+      <c r="F56" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
+        </is>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>lose 5 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>cactus_maze</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>3.3.3</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Follow the voice</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr"/>
+      <c r="F57" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>At the heart of the maze, the voice belongs to an old cactus in bloom. As its spines take another {n} HP, it drops something warm into your hands: the Cactus Heart. When you look up, the way out is right behind you.</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>lose 1-3 HP at random (can kill); the artifact cactus_heart</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>shrinking_pond</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>0 Water</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>The spirit gulps it down and splutters. "That's not even WET! You dried-up old prune!" A thirst settles in your throat that no water will fix: Ever Thirsting clings to you.</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>the spell you picked is gone for the run; the artifact ever_thirsting</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>shrinking_pond</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>1 Water</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>"Oh! A little drop. Thank you." The spirit pushes a few golden leaves out of the mud for you: 50 Leaves.</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>the spell you picked is gone for the run; +50 Leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>shrinking_pond</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>2 Water</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>"Ahh, that's lovely! Thank you, thank you!" The pond rises a finger's width, and the spirit fishes something out of the bottom for you: an artifact.</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>the spell you picked is gone for the run; a random common artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>shrinking_pond</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>3+ Water</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>The pond swells to its banks with a happy gurgle. The spirit rises up, beaming, and lays a treasure in your hands: a rare artifact.</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>the spell you picked is gone for the run; a random rare artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>shrinking_pond</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr"/>
+      <c r="F62" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>As you turn to leave, the spirit whispers something after you. Your throat goes dry, and it stays dry: Ever Thirsting clings to you.</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>the artifact ever_thirsting</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Stay awhile and listen</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr"/>
+      <c r="F63" s="14" t="inlineStr"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>The priest's eyes light up with delight, as if a century of life had dawned upon him again. His voice rings like a golden bell, full of vigor and pride:
+In ages beyond time, when the world was young and life was younger, a door in heaven opened, and through it slipped a small child. Her name was Aole. By her look, she had seen no more than thirteen winters, and her garb was that of a humble traveler. But judge not a book by its cover, for under that insignificant disguise was the soul of an outer god: a being of vast power and knowledge, who could create, shape and destroy worlds. Worlds like ours, no less.
+Yet she treated us as nothing but equals. She threw her wings away to walk this path of suffering and struggle alongside us mortals. For countless years, she broke bread with the poorest, held hands with the sickest and cried with the most unfortunate. She was a shield unto the weak and a sword unto the wicked.
+Her teaching was one of profound simplicity: be kind to one another, and to yourself. Surely in those mundane words lay boundless wisdom, for they were truly the only secret to the happiness of all.</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Go on...</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr"/>
+      <c r="F64" s="14" t="inlineStr"/>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>Then she lifted her eyes to the whole of creation, beholding it bound in chains of evil and tyranny, from the roots of the mountains to the edges of the sky. She grieved, saying: "I shall break this prison and set all creation free."
+With her rode the Four Horsemen, mighty in power, yet mightier still in devotion. One possessed the hands of a maestro, which could weave life itself into music. One had eyes so sharp that they pierced through all lies and liars alike. One had a beauty so radiant that a mere gaze upon her visage was enough to heal a broken heart. But none could compare to her first horseman, her first disciple, Adam. He needed no sword nor shield, for his devotion to Aole alone saved him from every evil that could befall him on his way.
+That was more than two hundred years ago. None of them returned. The faithful scattered like leaves before the storm, until only I remained to sweep the floor of her house.
+Yet what is life without faith? I have faith in Aole, and I have faith in you, traveler. Be kind to others and to yourself, and Aole's blessing is upon you. Amen.</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Thank you, father</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr"/>
+      <c r="F65" s="14" t="inlineStr"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>The priest falls silent, and peers at you over his spectacles. "Tell me, stranger: who was Aole?"</t>
+        </is>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Our lord and saviour</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr"/>
+      <c r="F66" s="14" t="inlineStr"/>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>"Yes! Yes, she was." The old man's eyes shine. "And why did she leave us?"</t>
+        </is>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>She abandoned us</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr"/>
+      <c r="F67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>To find a way to save this world from evil and tyranny</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr"/>
+      <c r="F68" s="14" t="inlineStr"/>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>"Just so, just so." He nods slowly. "And what, then, should a follower of Aole do?"</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2.1</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>Fight evil</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr"/>
+      <c r="F69" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2.2</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Show others kindness</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr"/>
+      <c r="F70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>Tears run down the old man's face. "You have listened with your heart. Take this, then, as she would have wanted." He lays his hands on yours, and you learn a spell: Aole's Blessing.</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>learn trade_winds (if you already have it: heal to full)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2.3</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr"/>
+      <c r="F71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.3</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr"/>
+      <c r="F72" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.2</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr"/>
+      <c r="F73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.3</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr"/>
+      <c r="F74" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr"/>
+      <c r="F75" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>"I understand, stranger," he says. "Bless your soul." As you leave, a warm breeze follows you down the road: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>flying_turtle</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>Help him</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr"/>
+      <c r="F76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>You flip the turtle back onto his feet. He shakes himself off and glares at you.
+"You think you've saved me, but you've only saved yourself from an inevitably painful future. Alright, I have no more use for you, you bipedal fool. Go on, git!"</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t>nothing</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>flying_turtle</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr"/>
+      <c r="F77" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>"Yeah, walk away, dummy. One of these days I'll fall on your head. You'll be enjoying the sunny weather when suddenly my heavily armored arse lands on your unflavored face. Maybe it'll look more appealing that way, with the imprint of my majestic behind on your visage. Walk away, dear dimwit. May the light somehow shine upon your bald head."</t>
+        </is>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>turtle_falls</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>Uh oh...</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr"/>
+      <c r="F78" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>WHAM! A heavily armored arse lands squarely on your face. The turtle bounces off, rights himself in mid-air and hovers there, cackling. "Told you so, potato head! Much better. Now that's a face with character!" He flies off into the sun. You lose 10 HP, and you will be wearing the imprint of his majestic behind for a while.</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>lose 10 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>mystery_shack</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>Side with the boy</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr"/>
+      <c r="F79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>The girl bursts into tears and runs away. The boy, very pleased with himself, rewards you with a crumpled dollar bill. Written across it: "Wow, this is worthless."</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>the artifact dollar_bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>mystery_shack</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>Side with the girl</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr"/>
+      <c r="F80" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>The boy stomps off, furious with you. The girl thanks you, and hands you the candy she was sucking on. It is half eaten, and a little sticky.</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>the artifact half_eaten_candy</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>mystery_shack</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>Give each of them a new toy, so they don't have to fight (give 2 artifacts)</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>you pick 2 artifacts to give (not curses); greyed out with fewer</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>The kids stop fighting at once to admire their new toys. They thank you together, and press a strange old book into your hands, a six-fingered hand drawn on its cover: the Mystery Book.</t>
+        </is>
+      </c>
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>the 2 artifacts you picked are gone; +1 Mystery Book (+1 spell slot, stacks; 3 of them teach Summoning Bill, which kills you)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>wax_witch</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>Give one drop of blood</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr"/>
+      <c r="F82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>A single drop of blood rises from your arm and drifts toward the witch. In mid-air it turns to purple wax, and seals itself onto your spell. You feel a little emptier: you lose {n} max HP.</t>
+        </is>
+      </c>
+      <c r="H82" s="13" t="inlineStr">
+        <is>
+          <t>1 drop(s): each loses 20% of max HP (rounded down); a purple wax seal per drop on the spell and Essence you pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>wax_witch</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Give two drops of blood</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr"/>
+      <c r="F83" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>Two drops of blood rise from your arm and drift toward the witch. In mid-air they turn to purple wax, and seal themselves onto your spells. You feel a lot emptier: you lose {n} max HP.</t>
+        </is>
+      </c>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t>2 drop(s): each loses 20% of max HP (rounded down); a purple wax seal per drop on the spell and Essence you pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>wax_witch</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr"/>
+      <c r="F84" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>You turn your back on the witch. The voice in your head chuckles softly, then falls silent.</t>
+        </is>
+      </c>
+      <c r="H84" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>Give him a spell</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>you pick one of your spells; greyed out if he has nothing to offer back</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
+        </is>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>it goes on his cart; you take 1 of 3 spells of the same rarity (bottles: same price range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>Give him an artifact</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>you pick one of your artifacts; greyed out if he has nothing to offer back</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
+        </is>
+      </c>
+      <c r="H86" s="13" t="inlineStr">
+        <is>
+          <t>it goes on his cart; you take 1 of 3 artifacts of the same rarity (bottles: same price range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>Give him a bottle</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>you pick one of your bottles; greyed out if he has nothing to offer back</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
+        </is>
+      </c>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>it goes on his cart; you take 1 of 3 bottles of the same rarity (bottles: same price range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>Give him nothing</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr"/>
+      <c r="F88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>"REDUCE!" he bellows, nodding as if you had done something very wise, and trundles off with his cart.</t>
+        </is>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>rolling_bear</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>Try to stop them</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr"/>
+      <c r="F89" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>They ram straight into you... It's a rolling bear! (bubble) "Thank you, stranger!" "Here, for your trouble." He presses 50 Leaves into your hand. Your ribs are less grateful: you lose 5 HP.</t>
+        </is>
+      </c>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>+50 Leaves; lose 5 HP (can kill). On the stage: he rolls into the middle and stops dead, upside down</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>rolling_bear</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>Get out of the way</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr"/>
+      <c r="F90" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>You step aside... (bubble) 'Why didn't you help me? Whyyyyyy...' His cry fades as he rolls further and further away.</t>
+        </is>
+      </c>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>the 3rd event from now is his revenge (any act). On the stage: he rolls off to the left</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>bear_revenge</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>Fight!</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr"/>
+      <c r="F91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>A ball of fur and muscle slams into you! (bubble) "Behold, heartless stranger!" "I have come for revenge!" You are still seeing stars: you will be Stunned for the first turn.</t>
+        </is>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>elite fight: Enraged Rolling Bear (elite rewards); you are Stunned on turn 1. On the stage: he rolls in from the right and slams into the middle</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>overgrown_vine</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>Cast a spell to help the tree</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell (you keep it)</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>Offensive spell</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>You blast the vine away. The tree sheds some leaves for you as its branches tremble with gratitude: 40 Leaves.</t>
+        </is>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>+40 Leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>overgrown_vine</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>Cast a spell to help the tree</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell (you keep it)</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="inlineStr">
+        <is>
+          <t>Defensive spell</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>You cast a barrier between the tree and the vine. The tree drops a fruit for you as its branches tremble with gratitude. You eat it and heal 5 HP.</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>heal 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>overgrown_vine</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>Cast a spell to help the tree</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell (you keep it)</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>Utility spell</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>Your spell does nothing. The tree is silently disappointed in your uselessness.</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>overgrown_vine</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>Leave the tree to its fate</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr"/>
+      <c r="F95" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>You walk on. Behind you, the branches creak a little louder.</t>
+        </is>
+      </c>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>broken_bridge</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>Jump over it</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr"/>
+      <c r="F96" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>You take a running start and leap. You make it across, heart pounding! You feel so excited that you will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>broken_bridge</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>Jump over it</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr"/>
+      <c r="F97" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>You take a running start and leap... and land with a splash in the middle of the bog. Your spellbook is soaked through: {spell} now needs 1 more Water.</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>a random active spell needs 1 more Water (added to the end of its pattern) for the run</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>broken_bridge</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>Find a way around the thorny bushes</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr"/>
+      <c r="F98" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>You push your way through the bushes until you find a way around. The thorns don't make it easy: you lose 5 HP.</t>
+        </is>
+      </c>
+      <c r="H98" s="13" t="inlineStr">
+        <is>
+          <t>lose 5 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Built from scripts/core/map_events.gd (the user's notes on the Events tab are canon). Blue = wording and numbers you can change.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Events 7-15 are still the old ones (to be rewritten later): their buttons still show what they do.</t>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Not reworked yet (old events, their buttons still show what they do): Golden Thicket, Old Spellbook, Squirrel Merchant, Tinker's Cart, Barterer, Upside-Down Pool, Wandering Apothecary.</t>
         </is>
       </c>
     </row>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4817,15 +4817,121 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>elemental_fishing</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>Help him fish</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr"/>
+      <c r="F99" s="14" t="inlineStr"/>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>"Wonderful!" He points a bony finger at the water. "The fish in this stream are made of Essence, so you catch them with a chant, not a rod. Line up your Essence and Chant: every fish loses the longest start of its row that your chant contains, just like in a fight. You can chant as often as you like, and your three Essence never run out. A whale is worth 10 Leaves, a swordfish 6 and a barracuda 4. You've got one minute!"</t>
+        </is>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>elemental_fishing</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr"/>
+      <c r="F100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>(the fishing, then the old man tallies the catch and pays)</t>
+        </is>
+      </c>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>60 s of chanting at Essence fish (one every ~6 s at first, 3 times as often by the end; 4 lanes, never a faster fish behind a slower one): whale (10 Essence, 24 s across) 10 Leaves, swordfish (4, 12 s) 6, barracuda (5, 16 s) 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>elemental_fishing</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr"/>
+      <c r="F101" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>"Oh, I see. You are busy," he sighs. "I will just wait another two hundred years, then."</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>Built from scripts/core/map_events.gd (the user's notes on the Events tab are canon). Blue = wording and numbers you can change.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>Not reworked yet (old events, their buttons still show what they do): Golden Thicket, Old Spellbook, Squirrel Merchant, Tinker's Cart, Barterer, Upside-Down Pool, Wandering Apothecary.</t>
         </is>

--- a/docs/events.xlsx
+++ b/docs/events.xlsx
@@ -8,8 +8,7 @@
   <sheets>
     <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Event script" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Options" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Room odds" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Room odds" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -525,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -617,7 +616,7 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>Choose one: (1) Pay 60 Leaves: a purple seal on 1 random spell that can still be sealed (that spell needs 1 Essence less). Greyed out if you have under 60 Leaves. (2) Heal 12 HP (never above your max). (3) Nothing.</t>
+          <t>See the Event script tab</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -655,7 +654,11 @@
       <c r="G3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="11" t="n"/>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>See the Event script tab</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
           <t>1) Help him confont the monster (immediately get into a mini boss fight, the wind sprite gives you 2 air to start the fight. Text: The monster is indeed very mean. Your new found friend tried his best to help you, which is not much). 2) Refuse to help (The wind sprite stopped crying, for he understood that it would do him no good and no one is going to help him (nothing happens to the player)</t>
@@ -693,7 +696,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Choose one: (1) 50/50: heal to full HP, or an ambush fight starts right away. (2) Nothing.</t>
+          <t>See the Event script tab</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -733,7 +736,7 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Choose one price, all for 1 random normal artifact you don't own (nothing if there's none left): (1) Lose 12 max HP (greyed out unless your max HP is over 17). (2) Lose 2 random spells from your spellbook for good (you always keep at least 1). (3) 2 random spells each need 1 more random Essence at the end of their pattern, for the run. (4) Nothing. Rarer than most events (weight 0.4).</t>
+          <t>See the Event script tab</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -773,7 +776,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Choose one: (1) Pay 35 Leaves: learn a random Legendary spell you've unlocked and don't have yet; if there is none you keep your Leaves. (2) Heal 5 HP.</t>
+          <t>See the Event script tab</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -813,7 +816,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Choose one: (1) Gain 1 random cursed artifact you don't own (+0 Leaves). (2) Heal 8 HP. Rarer than most events (weight 0.4).</t>
+          <t>See the Event script tab</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -828,32 +831,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>amber_vein</t>
+          <t>lost_camp</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>A Golden Thicket</t>
+          <t>An Abandoned Camp</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Golden leaves have drifted deep under a bramble. They look valuable, and the bramble looks extremely sharp.</t>
+          <t>The camp is in such bad shape that calling it a camp would be almost dishonest. A ring of soot, half a log, and a bedroll that has seen better centuries. But it is STILL a camp!</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <f>E8/SUM($E$2:$E$16)</f>
+        <f>E13/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Choose one: (1) Lose 5 HP: +45 Leaves. Greyed out unless you have more than 5 HP. (2) Nothing.</t>
+          <t>See the Event script tab</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -864,24 +867,24 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>old_tome</t>
+          <t>note_to_self</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>An Old Spellbook</t>
+          <t>A Note to Yourself</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>A book lies open on a stone, its pages turning by themselves. Reading it would cost you something.</t>
+          <t>A folded note is pinned to a tree, in handwriting you know very well. "Thought you might need this. Leave one for next time."</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4">
-        <f>E9/SUM($E$2:$E$16)</f>
+        <f>E16/SUM($E$2:$E$16)</f>
         <v/>
       </c>
       <c r="G9" s="2" t="n">
@@ -889,284 +892,36 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Choose one: (1) Lose 10 max HP: purple seals on 2 random spells (each needs 1 Essence less). Greyed out unless your max HP is over 15. (2) Nothing.</t>
+          <t>See the Event script tab</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>squirrel</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>A Squirrel Merchant</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>A squirrel in a tiny waistcoat offers you a very special acorn.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4">
-        <f>E10/SUM($E$2:$E$16)</f>
-        <v/>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>Choose one: (1) Pay 25 Leaves: +6 max HP (and +6 HP). (2) Nothing.</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n"/>
-    </row>
+    <row r="10"/>
     <row r="11" ht="28.5" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>tinker</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>The Tinker's Cart</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>A gnome with a hundred tiny tools squints at your pack. "I can make any of those better. For a price, naturally."</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4">
-        <f>E11/SUM($E$2:$E$16)</f>
-        <v/>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Choose one: (1) Pay 40 Leaves: 1 random artifact of yours that has a + version becomes its + version. Greyed out if none can be upgraded. (2) Nothing.</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="42.75" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>barterer</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>The Barterer</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>An old tortoise wears a shell piled high with trinkets. "Two of yours for one of mine. Mine are better. Mostly."</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4">
-        <f>E12/SUM($E$2:$E$16)</f>
-        <v/>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Choose one: (1) Pick 2 of your artifacts of the same tier and give them away, then pick 1 of 3 artifacts of the next tier up. Backing out at any step cancels the trade. Greyed out if you have no pair to trade. (2) Nothing.</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Blue text = values you can change. Yellow = your notes. Black = from the game / formulas.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28.5" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>lost_camp</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>An Abandoned Camp</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Someone left in a hurry. The fire is still warm, and there is a pouch by the bedroll.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4">
-        <f>E13/SUM($E$2:$E$16)</f>
-        <v/>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>Choose one: (1) Heal 10 HP. (2) +30 Leaves. (3) 1 random bottle (only if a bottle slot is free).</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="42.75" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>inverted_pool</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>The Upside-Down Pool</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>A still pool shows your spells upside down. It whispers that it could make one of them so, for good, if you let it drink.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4">
-        <f>E14/SUM($E$2:$E$16)</f>
-        <v/>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>Choose one: (1) Pick a spell (not a Power) and lose half your current HP (rounded down): for the rest of the run that spell plays as an anti-spell (or an anti-spell as a normal spell). Greyed out under 2 HP. (2) Nothing.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="28.5" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>apothecary</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>A Wandering Apothecary</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>A mole in thick spectacles rattles a cart full of little glass bottles. "Panic, bottled! Very reasonably priced."</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4">
-        <f>E15/SUM($E$2:$E$16)</f>
-        <v/>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Choose one: (1) Pay 25 Leaves: 2 random bottles (as many as your free slots hold; slots full: you keep your Leaves). (2) Lose 3 HP: 1 random bottle. (3) Nothing.</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="57" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>note_to_self</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>A Note to Yourself</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>A folded note is pinned to a tree, in handwriting you know very well. "Thought you might need this. Leave one for next time."</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4">
-        <f>E16/SUM($E$2:$E$16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>Choose one: (1) Take the spell waiting in the note into your spellbook (and active row if there's room), then pick one of your spells (not a fused one) to leave in the note: it leaves your spellbook and is kept in the save file, so a later run finds it. It's stored plain (no seals, curses or inversion). The very first note on a save holds Aole's Blessing. (2) Nothing.</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Blue text = values you can change. Yellow = your notes. Black = from the game / formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Source: scripts/core/map_events.gd (+ what each option does: RunState._do_event_option and the pick screens in main.gd), updated 2026-10-29.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Source: scripts/core/map_events.gd. Every event in the game is now one you designed; the Event script tab has all of them, with what each choice does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42.75" customHeight="1"/>
+    <row r="15" ht="28.5" customHeight="1"/>
+    <row r="16" ht="57" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1179,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2159,12 +1914,12 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>amber_vein</t>
+          <t>lost_camp</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -2174,33 +1929,37 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Reach in (lose 5 HP): +45 Leaves</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr"/>
+          <t>Half-cook some spells</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>greyed out without 2 spells that can be fused</t>
+        </is>
+      </c>
       <c r="F27" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>The fire sputters out before your spells are quite done. They are fused all the same, but no wax came of it.</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>amber</t>
+          <t>the campfire's fusing of 2 spells, but no wax seal</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>amber_vein</t>
+          <t>lost_camp</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -2210,28 +1969,28 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Admire it and move on</t>
+          <t>Rest restlessly</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr"/>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>You toss and turn on the lumpy ground, and wake up stiff all over. Still, it helped a little: you heal {n} HP.</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>heal half a campfire rest (15% of max HP, rounded down)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>old_tome</t>
+          <t>note_to_self</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -2246,7 +2005,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Read it (lose 10 max HP): 2 random spells need 1 Essence less</t>
+          <t>Take the spell in the note, and leave one of yours in it</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr"/>
@@ -2260,14 +2019,14 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>note_swap</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>old_tome</t>
+          <t>note_to_self</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -2282,7 +2041,7 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Close it gently</t>
+          <t>Leave the note for another day</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr"/>
@@ -2303,7 +2062,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>squirrel</t>
+          <t>farmer_farm</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -2318,28 +2077,26 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>Buy it for 25 Leaves (+6 max HP)</t>
+          <t>Of course</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr"/>
-      <c r="F31" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="F31" s="14" t="inlineStr"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>"Bless you!" The farmer is on his feet at once. "They're goblins. They pop up out of the wheat to nibble the ears, then duck back down. Shoot every one you see and I'll give you a Leaf a head. The big ones are hobgoblins: they take three shots, but they're worth 5 apiece. But mind the green ones! Those are the fairies who look after my fields, and every one you shoot will cost you 2 Leaves. You've got one minute before they eat the lot."</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>max_hp</t>
+          <t>opens a second page</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>squirrel</t>
+          <t>farmer_farm</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
@@ -2349,12 +2106,12 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Politely decline</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr"/>
@@ -2363,19 +2120,19 @@
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>(the mini game, then the farmer tallies how many goblins, hobgoblins and fairies, and the Leaves)</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>60 s shooting in the wheat: goblin +1, hobgoblin (3 shots) +5, fairy -2 Leaves; fairies 20% of the heads at the start, 35% at the end; never below 0 Leaves</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>tinker</t>
+          <t>farmer_farm</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -2385,33 +2142,33 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>Pay 40 Leaves: upgrade a random artifact</t>
+          <t>No way! I'm too busy to deal with peasants' problems</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr"/>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>"I see," says the farmer quietly, and goes back to staring at his wheat. You walk on.</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>upgrade_artifact</t>
+          <t>nothing</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>tinker</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -2421,33 +2178,37 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>No thank you</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr"/>
-      <c r="F34" s="14" t="n">
+          <t>Ignite a spell to burn a way out</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>the spell you picked is gone for the run</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>barterer</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -2457,33 +2218,33 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>Trade 2 artifacts of the same tier for 1 of the next tier</t>
+          <t>Force your way out</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr"/>
-      <c r="F35" s="14" t="n">
+      <c r="F35" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>trade_artifacts</t>
+          <t>lose 5 HP (can kill)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>barterer</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -2493,88 +2254,88 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Keep what you have</t>
+          <t>Follow the voice</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr"/>
-      <c r="F36" s="14" t="n">
+      <c r="F36" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>You squeeze between the cacti towards the humming. The spines catch you on the way: you lose {n} HP. The voice is closer now, but so are the walls.</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>lose 1-3 HP at random (can kill); then the same choices again</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>lost_camp</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>Half-cook some spells</t>
+          <t>Ignite a spell to burn a way out</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>greyed out without 2 spells that can be fused</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>The fire sputters out before your spells are quite done. They are fused all the same, but no wax came of it.</t>
+          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>the campfire's fusing of 2 spells, but no wax seal</t>
+          <t>the spell you picked is gone for the run</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>lost_camp</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Rest restlessly</t>
+          <t>Force your way out</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr"/>
@@ -2583,19 +2344,19 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>You toss and turn on the lumpy ground, and wake up stiff all over. Still, it helped a little: you heal {n} HP.</t>
+          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>heal half a campfire rest (15% of max HP, rounded down)</t>
+          <t>lose 5 HP (can kill)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>inverted_pool</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -2605,33 +2366,33 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>Let it drink half your HP: invert a spell (a spell becomes an anti-spell, an anti-spell a spell)</t>
+          <t>Follow the voice</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr"/>
-      <c r="F39" s="14" t="n">
+      <c r="F39" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>Deeper still. More spines, another {n} HP. The humming has turned into words you can almost understand.</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>invert_spell</t>
+          <t>lose 1-3 HP at random (can kill); then the same choices again</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>inverted_pool</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -2641,33 +2402,37 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Step back from the edge</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr"/>
-      <c r="F40" s="14" t="n">
+          <t>Ignite a spell to burn a way out</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>the spell you picked is gone for the run</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>apothecary</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -2677,33 +2442,33 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>Pay 25 Leaves: 2 random bottles</t>
+          <t>Force your way out</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr"/>
-      <c r="F41" s="14" t="n">
+      <c r="F41" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>bottle</t>
+          <t>lose 5 HP (can kill)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>apothecary</t>
+          <t>cactus_maze</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -2713,33 +2478,33 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Ask for a free sample (lose 3 HP): a random bottle</t>
+          <t>Follow the voice</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr"/>
-      <c r="F42" s="14" t="n">
+      <c r="F42" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>At the heart of the maze, the voice belongs to an old cactus in bloom. As its spines take another {n} HP, it drops something warm into your hands: the Cactus Heart. When you look up, the way out is right behind you.</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>bottle</t>
+          <t>lose 1-3 HP at random (can kill); the artifact cactus_heart</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>apothecary</t>
+          <t>shrinking_pond</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -2749,33 +2514,39 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>Walk on</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="14" t="n">
-        <v>1</v>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>0 Water</t>
+        </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>The spirit gulps it down and splutters. "That's not even WET! You dried-up old prune!" A thirst settles in your throat that no water will fix: Ever Thirsting clings to you.</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>the spell you picked is gone for the run; the artifact ever_thirsting</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>note_to_self</t>
+          <t>shrinking_pond</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -2790,28 +2561,34 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Take the spell in the note, and leave one of yours in it</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="14" t="n">
-        <v>1</v>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>1 Water</t>
+        </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>"Oh! A little drop. Thank you." The spirit pushes a few golden leaves out of the mud for you: 50 Leaves.</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>note_swap</t>
+          <t>the spell you picked is gone for the run; +50 Leaves</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>note_to_self</t>
+          <t>shrinking_pond</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -2821,33 +2598,39 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>Leave the note for another day</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr"/>
-      <c r="F45" s="14" t="n">
-        <v>1</v>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>2 Water</t>
+        </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>(not written yet: old event, shows the button's numbers)</t>
+          <t>"Ahh, that's lovely! Thank you, thank you!" The pond rises a finger's width, and the spirit fishes something out of the bottom for you: an artifact.</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>the spell you picked is gone for the run; a random common artifact</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>farmer_farm</t>
+          <t>shrinking_pond</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -2862,26 +2645,34 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Of course</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="14" t="inlineStr"/>
+          <t>Give it a spell</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell; greyed out with only one</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>3+ Water</t>
+        </is>
+      </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>"Bless you!" The farmer is on his feet at once. "They're goblins. They pop up out of the wheat to nibble the ears, then duck back down. Shoot every one you see and I'll give you a Leaf a head. The big ones are hobgoblins: they take three shots, but they're worth 5 apiece. But mind the green ones! Those are the fairies who look after my fields, and every one you shoot will cost you 2 Leaves. You've got one minute before they eat the lot."</t>
+          <t>The pond swells to its banks with a happy gurgle. The spirit rises up, beaming, and lays a treasure in your hands: a rare artifact.</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>opens a second page</t>
+          <t>the spell you picked is gone for the run; a random rare artifact</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>farmer_farm</t>
+          <t>shrinking_pond</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -2891,33 +2682,33 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Walk away</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr"/>
-      <c r="F47" s="14" t="n">
+      <c r="F47" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>(the mini game, then the farmer tallies how many goblins, hobgoblins and fairies, and the Leaves)</t>
+          <t>As you turn to leave, the spirit whispers something after you. Your throat goes dry, and it stays dry: Ever Thirsting clings to you.</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>60 s shooting in the wheat: goblin +1, hobgoblin (3 shots) +5, fairy -2 Leaves; fairies 20% of the heads at the start, 35% at the end; never below 0 Leaves</t>
+          <t>the artifact ever_thirsting</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>farmer_farm</t>
+          <t>church_of_aole</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -2927,593 +2718,17 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>No way! I'm too busy to deal with peasants' problems</t>
+          <t>Stay awhile and listen</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr"/>
-      <c r="F48" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="F48" s="14" t="inlineStr"/>
       <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>"I see," says the farmer quietly, and goes back to staring at his wheat. You walk on.</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>Ignite a spell to burn a way out</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell; greyed out with only one</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
-        </is>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>the spell you picked is gone for the run</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Force your way out</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr"/>
-      <c r="F50" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>lose 5 HP (can kill)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>Follow the voice</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr"/>
-      <c r="F51" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>You squeeze between the cacti towards the humming. The spines catch you on the way: you lose {n} HP. The voice is closer now, but so are the walls.</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>lose 1-3 HP at random (can kill); then the same choices again</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>Ignite a spell to burn a way out</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell; greyed out with only one</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>the spell you picked is gone for the run</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>Force your way out</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr"/>
-      <c r="F53" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
-        </is>
-      </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>lose 5 HP (can kill)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C54" s="13" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="D54" s="14" t="inlineStr">
-        <is>
-          <t>Follow the voice</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr"/>
-      <c r="F54" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>Deeper still. More spines, another {n} HP. The humming has turned into words you can almost understand.</t>
-        </is>
-      </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>lose 1-3 HP at random (can kill); then the same choices again</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>3.3.1</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>Ignite a spell to burn a way out</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell; greyed out with only one</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>{spell} goes up in flames, and the fire eats a path straight through the cactus. You walk out, smelling of smoke.</t>
-        </is>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>the spell you picked is gone for the run</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>3.3.2</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>Force your way out</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr"/>
-      <c r="F56" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>You push through the spines until you come out the other side. It hurts: you lose 5 HP.</t>
-        </is>
-      </c>
-      <c r="H56" s="13" t="inlineStr">
-        <is>
-          <t>lose 5 HP (can kill)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>cactus_maze</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>3.3.3</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>Follow the voice</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr"/>
-      <c r="F57" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>At the heart of the maze, the voice belongs to an old cactus in bloom. As its spines take another {n} HP, it drops something warm into your hands: the Cactus Heart. When you look up, the way out is right behind you.</t>
-        </is>
-      </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>lose 1-3 HP at random (can kill); the artifact cactus_heart</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>shrinking_pond</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>Give it a spell</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell; greyed out with only one</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>0 Water</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>The spirit gulps it down and splutters. "That's not even WET! You dried-up old prune!" A thirst settles in your throat that no water will fix: Ever Thirsting clings to you.</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>the spell you picked is gone for the run; the artifact ever_thirsting</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>shrinking_pond</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>Give it a spell</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell; greyed out with only one</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>1 Water</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>"Oh! A little drop. Thank you." The spirit pushes a few golden leaves out of the mud for you: 50 Leaves.</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>the spell you picked is gone for the run; +50 Leaves</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>shrinking_pond</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>Give it a spell</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell; greyed out with only one</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>2 Water</t>
-        </is>
-      </c>
-      <c r="G60" s="14" t="inlineStr">
-        <is>
-          <t>"Ahh, that's lovely! Thank you, thank you!" The pond rises a finger's width, and the spirit fishes something out of the bottom for you: an artifact.</t>
-        </is>
-      </c>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>the spell you picked is gone for the run; a random common artifact</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>shrinking_pond</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>Give it a spell</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell; greyed out with only one</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
-        <is>
-          <t>3+ Water</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr">
-        <is>
-          <t>The pond swells to its banks with a happy gurgle. The spirit rises up, beaming, and lays a treasure in your hands: a rare artifact.</t>
-        </is>
-      </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>the spell you picked is gone for the run; a random rare artifact</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>shrinking_pond</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D62" s="14" t="inlineStr">
-        <is>
-          <t>Walk away</t>
-        </is>
-      </c>
-      <c r="E62" s="13" t="inlineStr"/>
-      <c r="F62" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>As you turn to leave, the spirit whispers something after you. Your throat goes dry, and it stays dry: Ever Thirsting clings to you.</t>
-        </is>
-      </c>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>the artifact ever_thirsting</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>church_of_aole</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>Stay awhile and listen</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr"/>
-      <c r="F63" s="14" t="inlineStr"/>
-      <c r="G63" s="14" t="inlineStr">
         <is>
           <t>The priest's eyes light up with delight, as if a century of life had dawned upon him again. His voice rings like a golden bell, full of vigor and pride:
 In ages beyond time, when the world was young and life was younger, a door in heaven opened, and through it slipped a small child. Her name was Aole. By her look, she had seen no more than thirteen winters, and her garb was that of a humble traveler. But judge not a book by its cover, for under that insignificant disguise was the soul of an outer god: a being of vast power and knowledge, who could create, shape and destroy worlds. Worlds like ours, no less.
@@ -3521,36 +2736,36 @@
 Her teaching was one of profound simplicity: be kind to one another, and to yourself. Surely in those mundane words lay boundless wisdom, for they were truly the only secret to the happiness of all.</t>
         </is>
       </c>
-      <c r="H63" s="13" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>opens a second page</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>church_of_aole</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Go on...</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr"/>
-      <c r="F64" s="14" t="inlineStr"/>
-      <c r="G64" s="14" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr"/>
+      <c r="F49" s="14" t="inlineStr"/>
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>Then she lifted her eyes to the whole of creation, beholding it bound in chains of evil and tyranny, from the roots of the mountains to the edges of the sky. She grieved, saying: "I shall break this prison and set all creation free."
 With her rode the Four Horsemen, mighty in power, yet mightier still in devotion. One possessed the hands of a maestro, which could weave life itself into music. One had eyes so sharp that they pierced through all lies and liars alike. One had a beauty so radiant that a mere gaze upon her visage was enough to heal a broken heart. But none could compare to her first horseman, her first disciple, Adam. He needed no sword nor shield, for his devotion to Aole alone saved him from every evil that could befall him on his way.
@@ -3558,16 +2773,551 @@
 Yet what is life without faith? I have faith in Aole, and I have faith in you, traveler. Be kind to others and to yourself, and Aole's blessing is upon you. Amen.</t>
         </is>
       </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Thank you, father</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr"/>
+      <c r="F50" s="14" t="inlineStr"/>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>The priest falls silent, and peers at you over his spectacles. "Tell me, stranger: who was Aole?"</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Our lord and saviour</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr"/>
+      <c r="F51" s="14" t="inlineStr"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>"Yes! Yes, she was." The old man's eyes shine. "And why did she leave us?"</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>She abandoned us</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr"/>
+      <c r="F52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>To find a way to save this world from evil and tyranny</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr"/>
+      <c r="F53" s="14" t="inlineStr"/>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>"Just so, just so." He nods slowly. "And what, then, should a follower of Aole do?"</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>opens a second page</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2.1</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Fight evil</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr"/>
+      <c r="F54" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2.2</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Show others kindness</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr"/>
+      <c r="F55" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>Tears run down the old man's face. "You have listened with your heart. Take this, then, as she would have wanted." He lays his hands on yours, and you learn a spell: Aole's Blessing.</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>learn trade_winds (if you already have it: heal to full)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.2.3</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr"/>
+      <c r="F56" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.1.3</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr"/>
+      <c r="F57" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.2</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr"/>
+      <c r="F58" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>1.1.1.3</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr"/>
+      <c r="F59" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>church_of_aole</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr"/>
+      <c r="F60" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>"I understand, stranger," he says. "Bless your soul." As you leave, a warm breeze follows you down the road: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>you start your next fight with 1 extra random Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>flying_turtle</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Help him</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr"/>
+      <c r="F61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>You flip the turtle back onto his feet. He shakes himself off and glares at you.
+"You think you've saved me, but you've only saved yourself from an inevitably painful future. Alright, I have no more use for you, you bipedal fool. Go on, git!"</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>flying_turtle</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr"/>
+      <c r="F62" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>"Yeah, walk away, dummy. One of these days I'll fall on your head. You'll be enjoying the sunny weather when suddenly my heavily armored arse lands on your unflavored face. Maybe it'll look more appealing that way, with the imprint of my majestic behind on your visage. Walk away, dear dimwit. May the light somehow shine upon your bald head."</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>turtle_falls</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Uh oh...</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr"/>
+      <c r="F63" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>WHAM! A heavily armored arse lands squarely on your face. The turtle bounces off, rights himself in mid-air and hovers there, cackling. "Told you so, potato head! Much better. Now that's a face with character!" He flies off into the sun. You lose 10 HP, and you will be wearing the imprint of his majestic behind for a while.</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>lose 10 HP (can kill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>mystery_shack</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Side with the boy</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr"/>
+      <c r="F64" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>The girl bursts into tears and runs away. The boy, very pleased with himself, rewards you with a crumpled dollar bill. Written across it: "Wow, this is worthless."</t>
+        </is>
+      </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>opens a second page</t>
+          <t>the artifact dollar_bill</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>mystery_shack</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -3577,31 +3327,33 @@
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D65" s="14" t="inlineStr">
         <is>
-          <t>Thank you, father</t>
+          <t>Side with the girl</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr"/>
-      <c r="F65" s="14" t="inlineStr"/>
+      <c r="F65" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>The priest falls silent, and peers at you over his spectacles. "Tell me, stranger: who was Aole?"</t>
+          <t>The boy stomps off, furious with you. The girl thanks you, and hands you the candy she was sucking on. It is half eaten, and a little sticky.</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>opens a second page</t>
+          <t>the artifact half_eaten_candy</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>mystery_shack</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -3611,46 +3363,52 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>Our lord and saviour</t>
-        </is>
-      </c>
-      <c r="E66" s="13" t="inlineStr"/>
-      <c r="F66" s="14" t="inlineStr"/>
+          <t>Give each of them a new toy, so they don't have to fight (give 2 artifacts)</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>you pick 2 artifacts to give (not curses); greyed out with fewer</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>"Yes! Yes, she was." The old man's eyes shine. "And why did she leave us?"</t>
+          <t>The kids stop fighting at once to admire their new toys. They thank you together, and press a strange old book into your hands, a six-fingered hand drawn on its cover: the Mystery Book.</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>opens a second page</t>
+          <t>the 2 artifacts you picked are gone; +1 Mystery Book (+1 spell slot, stacks; 3 of them teach Summoning Bill, which kills you)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>wax_witch</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>She abandoned us</t>
+          <t>Give one drop of blood</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr"/>
@@ -3659,68 +3417,70 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+          <t>A single drop of blood rises from your arm and drifts toward the witch. In mid-air it turns to purple wax, and seals itself onto your spell. You feel a little emptier: you lose {n} max HP.</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>you start your next fight with 1 extra random Essence</t>
+          <t>1 drop(s): each loses 20% of max HP (rounded down); a purple wax seal per drop on the spell and Essence you pick</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>wax_witch</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>To find a way to save this world from evil and tyranny</t>
+          <t>Give two drops of blood</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr"/>
-      <c r="F68" s="14" t="inlineStr"/>
+      <c r="F68" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>"Just so, just so." He nods slowly. "And what, then, should a follower of Aole do?"</t>
+          <t>Two drops of blood rise from your arm and drift toward the witch. In mid-air they turn to purple wax, and seal themselves onto your spells. You feel a lot emptier: you lose {n} max HP.</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>opens a second page</t>
+          <t>2 drop(s): each loses 20% of max HP (rounded down); a purple wax seal per drop on the spell and Essence you pick</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>wax_witch</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.1.2.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>Fight evil</t>
+          <t>Walk away</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr"/>
@@ -3729,142 +3489,154 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+          <t>You turn your back on the witch. The voice in your head chuckles softly, then falls silent.</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>you start your next fight with 1 extra random Essence</t>
+          <t>nothing</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>recycler</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.1.2.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Show others kindness</t>
-        </is>
-      </c>
-      <c r="E70" s="13" t="inlineStr"/>
-      <c r="F70" s="15" t="n">
+          <t>Give him a spell</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>you pick one of your spells; greyed out if he has nothing to offer back</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>Tears run down the old man's face. "You have listened with your heart. Take this, then, as she would have wanted." He lays his hands on yours, and you learn a spell: Aole's Blessing.</t>
+          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>learn trade_winds (if you already have it: heal to full)</t>
+          <t>it goes on his cart; you take 1 of 3 spells of the same rarity (bottles: same price range)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>recycler</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.1.2.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="inlineStr"/>
-      <c r="F71" s="15" t="n">
+          <t>Give him an artifact</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>you pick one of your artifacts; greyed out if he has nothing to offer back</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t>you start your next fight with 1 extra random Essence</t>
+          <t>it goes on his cart; you take 1 of 3 artifacts of the same rarity (bottles: same price range)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>recycler</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.1.3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>I don't know</t>
-        </is>
-      </c>
-      <c r="E72" s="13" t="inlineStr"/>
-      <c r="F72" s="15" t="n">
+          <t>Give him a bottle</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>you pick one of your bottles; greyed out if he has nothing to offer back</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>you start your next fight with 1 extra random Essence</t>
+          <t>it goes on his cart; you take 1 of 3 bottles of the same rarity (bottles: same price range)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>recycler</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>I don't know</t>
+          <t>Give him nothing</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr"/>
@@ -3873,19 +3645,19 @@
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+          <t>"REDUCE!" he bellows, nodding as if you had done something very wise, and trundles off with his cart.</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>you start your next fight with 1 extra random Essence</t>
+          <t>nothing</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>rolling_bear</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -3895,33 +3667,33 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>1.1.1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Try to stop them</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr"/>
-      <c r="F74" s="15" t="n">
+      <c r="F74" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>The old priest's face falls, but he smiles at you all the same. "I understand, stranger. Bless your soul." A warm breeze follows you out of the church: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+          <t>They ram straight into you... It's a rolling bear! (bubble) "Thank you, stranger!" "Here, for your trouble." He presses 50 Leaves into your hand. Your ribs are less grateful: you lose 5 HP.</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>you start your next fight with 1 extra random Essence</t>
+          <t>+50 Leaves; lose 5 HP (can kill). On the stage: he rolls into the middle and stops dead, upside down</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>church_of_aole</t>
+          <t>rolling_bear</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -3936,33 +3708,33 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>Walk away</t>
+          <t>Get out of the way</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr"/>
-      <c r="F75" s="15" t="n">
+      <c r="F75" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>"I understand, stranger," he says. "Bless your soul." As you leave, a warm breeze follows you down the road: Aole's Small Blessing. You will start your next fight with 1 extra random Essence.</t>
+          <t>You step aside... (bubble) 'Why didn't you help me? Whyyyyyy...' His cry fades as he rolls further and further away.</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>you start your next fight with 1 extra random Essence</t>
+          <t>the 3rd event from now is his revenge (any act). On the stage: he rolls off to the left</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>flying_turtle</t>
+          <t>bear_revenge</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -3972,29 +3744,28 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>Help him</t>
+          <t>Fight!</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr"/>
-      <c r="F76" s="15" t="n">
+      <c r="F76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>You flip the turtle back onto his feet. He shakes himself off and glares at you.
-"You think you've saved me, but you've only saved yourself from an inevitably painful future. Alright, I have no more use for you, you bipedal fool. Go on, git!"</t>
+          <t>A ball of fur and muscle slams into you! (bubble) "Behold, heartless stranger!" "I have come for revenge!" You are still seeing stars: you will be Stunned for the first turn.</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>elite fight: Enraged Rolling Bear (elite rewards); you are Stunned on turn 1. On the stage: he rolls in from the right and slams into the middle</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>flying_turtle</t>
+          <t>overgrown_vine</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -4004,38 +3775,44 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>Walk away</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr"/>
-      <c r="F77" s="15" t="n">
-        <v>1</v>
+          <t>Cast a spell to help the tree</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell (you keep it)</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>Offensive spell</t>
+        </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>"Yeah, walk away, dummy. One of these days I'll fall on your head. You'll be enjoying the sunny weather when suddenly my heavily armored arse lands on your unflavored face. Maybe it'll look more appealing that way, with the imprint of my majestic behind on your visage. Walk away, dear dimwit. May the light somehow shine upon your bald head."</t>
+          <t>You blast the vine away. The tree sheds some leaves for you as its branches tremble with gratitude: 40 Leaves.</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>+40 Leaves</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>turtle_falls</t>
+          <t>overgrown_vine</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -4045,28 +3822,34 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Uh oh...</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr"/>
-      <c r="F78" s="15" t="n">
-        <v>1</v>
+          <t>Cast a spell to help the tree</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell (you keep it)</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>Defensive spell</t>
+        </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>WHAM! A heavily armored arse lands squarely on your face. The turtle bounces off, rights himself in mid-air and hovers there, cackling. "Told you so, potato head! Much better. Now that's a face with character!" He flies off into the sun. You lose 10 HP, and you will be wearing the imprint of his majestic behind for a while.</t>
+          <t>You cast a barrier between the tree and the vine. The tree drops a fruit for you as its branches tremble with gratitude. You eat it and heal 5 HP.</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>lose 10 HP (can kill)</t>
+          <t>heal 5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>mystery_shack</t>
+          <t>overgrown_vine</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -4081,28 +3864,34 @@
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>Side with the boy</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr"/>
-      <c r="F79" s="15" t="n">
-        <v>1</v>
+          <t>Cast a spell to help the tree</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>you pick a spell (you keep it)</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>Utility spell</t>
+        </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
-          <t>The girl bursts into tears and runs away. The boy, very pleased with himself, rewards you with a crumpled dollar bill. Written across it: "Wow, this is worthless."</t>
+          <t>Your spell does nothing. The tree is silently disappointed in your uselessness.</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>the artifact dollar_bill</t>
+          <t>nothing</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>mystery_shack</t>
+          <t>overgrown_vine</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
@@ -4117,7 +3906,7 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>Side with the girl</t>
+          <t>Leave the tree to its fate</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr"/>
@@ -4126,64 +3915,60 @@
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>The boy stomps off, furious with you. The girl thanks you, and hands you the candy she was sucking on. It is half eaten, and a little sticky.</t>
+          <t>You walk on. Behind you, the branches creak a little louder.</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t>the artifact half_eaten_candy</t>
+          <t>nothing</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>mystery_shack</t>
+          <t>broken_bridge</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>Give each of them a new toy, so they don't have to fight (give 2 artifacts)</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
-        <is>
-          <t>you pick 2 artifacts to give (not curses); greyed out with fewer</t>
-        </is>
-      </c>
+          <t>Jump over it</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr"/>
       <c r="F81" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
-          <t>The kids stop fighting at once to admire their new toys. They thank you together, and press a strange old book into your hands, a six-fingered hand drawn on its cover: the Mystery Book.</t>
+          <t>You take a running start and leap. You make it across, heart pounding! You feel so excited that you will start your next fight with 1 extra random Essence.</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>the 2 artifacts you picked are gone; +1 Mystery Book (+1 spell slot, stacks; 3 of them teach Summoning Bill, which kills you)</t>
+          <t>you start your next fight with 1 extra random Essence</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>wax_witch</t>
+          <t>broken_bridge</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -4193,33 +3978,33 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Give one drop of blood</t>
+          <t>Jump over it</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr"/>
       <c r="F82" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>A single drop of blood rises from your arm and drifts toward the witch. In mid-air it turns to purple wax, and seals itself onto your spell. You feel a little emptier: you lose {n} max HP.</t>
+          <t>You take a running start and leap... and land with a splash in the middle of the bog. Your spellbook is soaked through: {spell} now needs 1 more Water.</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>1 drop(s): each loses 20% of max HP (rounded down); a purple wax seal per drop on the spell and Essence you pick</t>
+          <t>a random active spell needs 1 more Water (added to the end of its pattern) for the run</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>wax_witch</t>
+          <t>broken_bridge</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -4229,7 +4014,7 @@
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>Give two drops of blood</t>
+          <t>Find a way around the thorny bushes</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr"/>
@@ -4238,100 +4023,94 @@
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>Two drops of blood rise from your arm and drift toward the witch. In mid-air they turn to purple wax, and seal themselves onto your spells. You feel a lot emptier: you lose {n} max HP.</t>
+          <t>You push your way through the bushes until you find a way around. The thorns don't make it easy: you lose 5 HP.</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>2 drop(s): each loses 20% of max HP (rounded down); a purple wax seal per drop on the spell and Essence you pick</t>
+          <t>lose 5 HP (can kill)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>wax_witch</t>
+          <t>elemental_fishing</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>Walk away</t>
+          <t>Help him fish</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr"/>
-      <c r="F84" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="F84" s="14" t="inlineStr"/>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>You turn your back on the witch. The voice in your head chuckles softly, then falls silent.</t>
+          <t>"Wonderful!" He points a bony finger at the water. "The fish in this stream are made of Essence, so you catch them with a chant, not a rod. Line up your Essence and Chant: every fish loses the longest start of its row that your chant contains, just like in a fight. You can chant as often as you like, and your three Essence never run out. A whale is worth 10 Leaves, a swordfish 6 and a barracuda 4. You've got one minute!"</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>opens a second page</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>recycler</t>
+          <t>elemental_fishing</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>Give him a spell</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="inlineStr">
-        <is>
-          <t>you pick one of your spells; greyed out if he has nothing to offer back</t>
-        </is>
-      </c>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr"/>
       <c r="F85" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
-          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
+          <t>(the fishing, then the old man tallies the catch and pays)</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>it goes on his cart; you take 1 of 3 spells of the same rarity (bottles: same price range)</t>
+          <t>60 s of chanting at Essence fish (one every ~6 s at first, 3 times as often by the end; 4 lanes, never a faster fish behind a slower one): whale (10 Essence, about 22 s across) 10 Leaves, swordfish (4, about 11 s) 6, barracuda (5, about 14.5 s) 4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>recycler</t>
+          <t>elemental_fishing</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -4341,87 +4120,79 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>Give him an artifact</t>
-        </is>
-      </c>
-      <c r="E86" s="13" t="inlineStr">
-        <is>
-          <t>you pick one of your artifacts; greyed out if he has nothing to offer back</t>
-        </is>
-      </c>
-      <c r="F86" s="14" t="n">
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr"/>
+      <c r="F86" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
-          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
+          <t>"Oh, I see. You are busy," he sighs. "I will just wait another two hundred years, then."</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
-          <t>it goes on his cart; you take 1 of 3 artifacts of the same rarity (bottles: same price range)</t>
+          <t>nothing</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>recycler</t>
+          <t>mausoleum</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>Give him a bottle</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr">
-        <is>
-          <t>you pick one of your bottles; greyed out if he has nothing to offer back</t>
-        </is>
-      </c>
-      <c r="F87" s="14" t="n">
+          <t>Touch the red ball</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr"/>
+      <c r="F87" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
-          <t>You take it. "REUSE!" he bellows approvingly, and trundles off with his cart. You can still hear him long after he is out of sight.</t>
+          <t>The red light floods into your veins, warm as a heartbeat. Somewhere in the coffin below, something sighs. You feel sturdier than ever: +{n} max HP.</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>it goes on his cart; you take 1 of 3 bottles of the same rarity (bottles: same price range)</t>
+          <t>+20% max HP (rounded down), healed as much</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>recycler</t>
+          <t>mausoleum</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>Give him nothing</t>
+          <t>Touch the blue ball</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr"/>
@@ -4430,174 +4201,168 @@
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>"REDUCE!" he bellows, nodding as if you had done something very wise, and trundles off with his cart.</t>
+          <t>The blue light settles over your skin like cold armour, and stays there, waiting. You will start your next fight with 20 Lasting Shield.</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>start your next fight with 20 Lasting Shield</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>rolling_bear</t>
+          <t>mausoleum</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>Try to stop them</t>
+          <t>Touch the green ball</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr"/>
-      <c r="F89" s="14" t="n">
+      <c r="F89" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>They ram straight into you... It's a rolling bear! (bubble) "Thank you, stranger!" "Here, for your trouble." He presses 50 Leaves into your hand. Your ribs are less grateful: you lose 5 HP.</t>
+          <t>The green light leaps into your bag and hides there, giggling. You will start your next fight with 3 extra random Essence.</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>+50 Leaves; lose 5 HP (can kill). On the stage: he rolls into the middle and stops dead, upside down</t>
+          <t>you start your next fight with 3 extra random Essence</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>rolling_bear</t>
+          <t>watchtower</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>Get out of the way</t>
+          <t>A camping site</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr"/>
-      <c r="F90" s="14" t="n">
+      <c r="F90" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>You step aside... (bubble) 'Why didn't you help me? Whyyyyyy...' His cry fades as he rolls further and further away.</t>
+          <t>A thin line of smoke rises from a clearing not far off. You climb down and make your way there: a campfire, still burning, and nobody around to mind it.</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
         <is>
-          <t>the 3rd event from now is his revenge (any act). On the stage: he rolls off to the left</t>
+          <t>go to a campfire</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>bear_revenge</t>
+          <t>watchtower</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>1, 2, 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>Fight!</t>
+          <t>A towering monster</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr"/>
-      <c r="F91" s="14" t="n">
+      <c r="F91" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
-          <t>A ball of fur and muscle slams into you! (bubble) "Behold, heartless stranger!" "I have come for revenge!" You are still seeing stars: you will be Stunned for the first turn.</t>
+          <t>Something enormous moves on the horizon. Before you are even halfway down the tower, it has seen you, and it is coming.</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>elite fight: Enraged Rolling Bear (elite rewards); you are Stunned on turn 1. On the stage: he rolls in from the right and slams into the middle</t>
+          <t>fight a random Act 1 boss: no talk first, full boss rewards, the act goes on</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>overgrown_vine</t>
+          <t>watchtower</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Cast a spell to help the tree</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell (you keep it)</t>
-        </is>
-      </c>
-      <c r="F92" s="14" t="inlineStr">
-        <is>
-          <t>Offensive spell</t>
-        </is>
+          <t>The merchant</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr"/>
+      <c r="F92" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>You blast the vine away. The tree sheds some leaves for you as its branches tremble with gratitude: 40 Leaves.</t>
+          <t>A familiar cart trundles along the road below. You hurry down the steps and wave it over.</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t>+40 Leaves</t>
+          <t>go to the merchant</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>overgrown_vine</t>
+          <t>skipping_stones</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -4607,64 +4372,48 @@
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>Cast a spell to help the tree</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell (you keep it)</t>
-        </is>
-      </c>
-      <c r="F93" s="14" t="inlineStr">
-        <is>
-          <t>Defensive spell</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>You cast a barrier between the tree and the vine. The tree drops a fruit for you as its branches tremble with gratitude. You eat it and heal 5 HP.</t>
-        </is>
-      </c>
+          <t>Skip a stone</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr"/>
+      <c r="F93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="14" t="inlineStr"/>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>heal 5</t>
+          <t>the stone skips 1-21 times (shown); 20 or more: a random common artifact and the event ends; otherwise skip another or walk away (10.5 throws on average)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>overgrown_vine</t>
+          <t>skipping_stones</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>Cast a spell to help the tree</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>you pick a spell (you keep it)</t>
-        </is>
-      </c>
-      <c r="F94" s="14" t="inlineStr">
-        <is>
-          <t>Utility spell</t>
-        </is>
+          <t>Walk away</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr"/>
+      <c r="F94" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Your spell does nothing. The tree is silently disappointed in your uselessness.</t>
+          <t>You dust off your hands and leave the lake to its stillness.</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
@@ -4673,267 +4422,10 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="13" t="inlineStr">
-        <is>
-          <t>overgrown_vine</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>Leave the tree to its fate</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="inlineStr"/>
-      <c r="F95" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>You walk on. Behind you, the branches creak a little louder.</t>
-        </is>
-      </c>
-      <c r="H95" s="13" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-    </row>
     <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>broken_bridge</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D96" s="14" t="inlineStr">
-        <is>
-          <t>Jump over it</t>
-        </is>
-      </c>
-      <c r="E96" s="13" t="inlineStr"/>
-      <c r="F96" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G96" s="14" t="inlineStr">
-        <is>
-          <t>You take a running start and leap. You make it across, heart pounding! You feel so excited that you will start your next fight with 1 extra random Essence.</t>
-        </is>
-      </c>
-      <c r="H96" s="13" t="inlineStr">
-        <is>
-          <t>you start your next fight with 1 extra random Essence</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="13" t="inlineStr">
-        <is>
-          <t>broken_bridge</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>Jump over it</t>
-        </is>
-      </c>
-      <c r="E97" s="13" t="inlineStr"/>
-      <c r="F97" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G97" s="14" t="inlineStr">
-        <is>
-          <t>You take a running start and leap... and land with a splash in the middle of the bog. Your spellbook is soaked through: {spell} now needs 1 more Water.</t>
-        </is>
-      </c>
-      <c r="H97" s="13" t="inlineStr">
-        <is>
-          <t>a random active spell needs 1 more Water (added to the end of its pattern) for the run</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
-        <is>
-          <t>broken_bridge</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C98" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D98" s="14" t="inlineStr">
-        <is>
-          <t>Find a way around the thorny bushes</t>
-        </is>
-      </c>
-      <c r="E98" s="13" t="inlineStr"/>
-      <c r="F98" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="14" t="inlineStr">
-        <is>
-          <t>You push your way through the bushes until you find a way around. The thorns don't make it easy: you lose 5 HP.</t>
-        </is>
-      </c>
-      <c r="H98" s="13" t="inlineStr">
-        <is>
-          <t>lose 5 HP (can kill)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="13" t="inlineStr">
-        <is>
-          <t>elemental_fishing</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>Help him fish</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="inlineStr"/>
-      <c r="F99" s="14" t="inlineStr"/>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>"Wonderful!" He points a bony finger at the water. "The fish in this stream are made of Essence, so you catch them with a chant, not a rod. Line up your Essence and Chant: every fish loses the longest start of its row that your chant contains, just like in a fight. You can chant as often as you like, and your three Essence never run out. A whale is worth 10 Leaves, a swordfish 6 and a barracuda 4. You've got one minute!"</t>
-        </is>
-      </c>
-      <c r="H99" s="13" t="inlineStr">
-        <is>
-          <t>opens a second page</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="13" t="inlineStr">
-        <is>
-          <t>elemental_fishing</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C100" s="13" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D100" s="14" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="E100" s="13" t="inlineStr"/>
-      <c r="F100" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="14" t="inlineStr">
-        <is>
-          <t>(the fishing, then the old man tallies the catch and pays)</t>
-        </is>
-      </c>
-      <c r="H100" s="13" t="inlineStr">
-        <is>
-          <t>60 s of chanting at Essence fish (one every ~6 s at first, 3 times as often by the end; 4 lanes, never a faster fish behind a slower one): whale (10 Essence, 24 s across) 10 Leaves, swordfish (4, 12 s) 6, barracuda (5, 16 s) 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="13" t="inlineStr">
-        <is>
-          <t>elemental_fishing</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D101" s="14" t="inlineStr">
-        <is>
-          <t>Walk away</t>
-        </is>
-      </c>
-      <c r="E101" s="13" t="inlineStr"/>
-      <c r="F101" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="14" t="inlineStr">
-        <is>
-          <t>"Oh, I see. You are busy," he sighs. "I will just wait another two hundred years, then."</t>
-        </is>
-      </c>
-      <c r="H101" s="13" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Built from scripts/core/map_events.gd (the user's notes on the Events tab are canon). Blue = wording and numbers you can change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Not reworked yet (old events, their buttons still show what they do): Golden Thicket, Old Spellbook, Squirrel Merchant, Tinker's Cart, Barterer, Upside-Down Pool, Wandering Apothecary.</t>
         </is>
       </c>
     </row>
@@ -4943,1529 +4435,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Event ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Event title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Opt</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Button text (shown to player)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cost type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Effect code</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>What it does</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Rarity / pool</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Your notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>The Whispering Well</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Drop in 60 Leaves (a random spell needs 1 Essence less)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Leaves</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>upgrade</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Upgrade n random spells (need 1 Essence less)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>The Whispering Well</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Drink deeply (heal 12)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>heal</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Heal n</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>The Whispering Well</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Walk on</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>lost_sprite</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A Lost Sprite</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Guide it home (lose 6 HP): learn a Rare spell</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>spell</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Learn a spell of a rarity</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>lost_sprite</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>A Lost Sprite</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Wish it luck and leave</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>mushroom_ring</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>The Mushroom Ring</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Dance! (half the time: heal to full; otherwise: an ambush)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>gamble</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>50%: heal to full, else an ambush fight</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>mushroom_ring</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>The Mushroom Ring</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Walk around it, very carefully</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>hollow_stump</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>The Hollow Stump</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Reach in and let it bite (lose 12 max HP): gain an artifact</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Max HP</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>artifact</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Gain an artifact from a pool</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="28.5" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>hollow_stump</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>The Hollow Stump</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Feed it 2 of your spells (2 random spells, gone): gain an artifact</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Lose random spells</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>artifact</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Gain an artifact from a pool</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="28.5" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>hollow_stump</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>The Hollow Stump</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Let its thorns tangle your spellbook (2 random spells need 1 more Essence): gain an artifact</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Spells +1 Essence</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>artifact</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Gain an artifact from a pool</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>hollow_stump</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>The Hollow Stump</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Leave it be</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>bard</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>A Travelling Bard</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Pay 35 Leaves: learn a Legendary spell</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Leaves</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>spell</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Learn a spell of a rarity</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>bard</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>A Travelling Bard</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Just listen for a while (heal 5)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>heal</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Heal n</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>cursed_shrine</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>A Cursed Shrine</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Take the idol: a cursed artifact</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>curse_amber</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>+n Leaves and a cursed artifact</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>cursed_shrine</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>A Cursed Shrine</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Pray instead (heal 8)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>heal</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Heal n</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>amber_vein</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>A Golden Thicket</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Reach in (lose 5 HP): +45 Leaves</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>+n Leaves</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>amber_vein</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>A Golden Thicket</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Admire it and move on</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="28.5" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>old_tome</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>An Old Spellbook</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Read it (lose 10 max HP): 2 random spells need 1 Essence less</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Max HP</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>upgrade</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Upgrade n random spells (need 1 Essence less)</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>old_tome</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>An Old Spellbook</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Close it gently</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>squirrel</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>A Squirrel Merchant</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Buy it for 25 Leaves (+6 max HP)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Leaves</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>max_hp</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>+n max HP</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>squirrel</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>A Squirrel Merchant</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Politely decline</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="28.5" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>tinker</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>The Tinker's Cart</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Pay 40 Leaves: upgrade a random artifact</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Leaves</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>upgrade_artifact</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Upgrade a random artifact</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>tinker</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>The Tinker's Cart</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>No thank you</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="28.5" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>barterer</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>The Barterer</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Trade 2 artifacts of the same tier for 1 of the next tier</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>trade_artifacts</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Give 2 artifacts of a tier, get 1 of the next</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>barterer</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>The Barterer</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Keep what you have</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>lost_camp</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>An Abandoned Camp</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Rest by the fire (heal 10)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>heal</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Heal n</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>lost_camp</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>An Abandoned Camp</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Search the pouch (+30 Leaves)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>+n Leaves</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>lost_camp</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>An Abandoned Camp</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Check the saddlebag (a random bottle)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>bottle</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>n random bottles</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="28.5" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>inverted_pool</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>The Upside-Down Pool</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Let it drink half your HP: invert a spell (a spell becomes an anti-spell, an anti-spell a spell)</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>% of current HP</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>invert_spell</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Invert a spell (spell &lt;-&gt; anti-spell)</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>inverted_pool</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>The Upside-Down Pool</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Step back from the edge</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="28.5" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>apothecary</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>A Wandering Apothecary</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Pay 25 Leaves: 2 random bottles</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Leaves</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>bottle</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>n random bottles</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="28.5" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>apothecary</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>A Wandering Apothecary</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Ask for a free sample (lose 3 HP): a random bottle</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>bottle</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>n random bottles</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="28.5" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>apothecary</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>A Wandering Apothecary</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Walk on</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="28.5" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>note_to_self</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>A Note to Yourself</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Take the spell in the note, and leave one of yours in it</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>note_swap</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Get the save's stored spell; store one of yours (pick) for a later run</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>note_to_self</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>A Note to Yourself</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Leave the note for another day</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="5" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
